--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486959_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486959_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. MUÑOZ SAMATAN</t>
+          <t>Y. KOLO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3321</v>
+        <v>3.3379</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8912</v>
+        <v>3.0708</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4409</v>
+        <v>0.2671</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1446</v>
+        <v>3.2023</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9205</v>
+        <v>0.6976</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2241</v>
+        <v>2.5047</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3065</v>
+        <v>3.4545</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1091</v>
+        <v>1.113</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1973</v>
+        <v>2.3415</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1619</v>
+        <v>-0.2522</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1887</v>
+        <v>-0.4154</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0268</v>
+        <v>0.1632</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4107</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6427</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5981</v>
+        <v>0.1356</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6381</v>
+        <v>-0.3836</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.04</v>
+        <v>0.5192</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Y. KOLO</t>
+          <t>D. MUÑOZ SAMATAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3658</v>
+        <v>2.4352</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8616</v>
+        <v>1.1129</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5042</v>
+        <v>1.3223</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2023</v>
+        <v>2.1446</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6976</v>
+        <v>1.9205</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5047</v>
+        <v>0.2241</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4545</v>
+        <v>2.3065</v>
       </c>
       <c r="K3" t="n">
-        <v>1.113</v>
+        <v>2.1091</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3415</v>
+        <v>0.1973</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2522</v>
+        <v>-0.1619</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4154</v>
+        <v>-0.1887</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1632</v>
+        <v>0.0268</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.6427</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1635</v>
+        <v>0.7013</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5928</v>
+        <v>0.8599</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7564</v>
+        <v>-0.1586</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3739</v>
+        <v>1.172</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6862</v>
+        <v>1.4843</v>
       </c>
       <c r="F4" t="n">
         <v>-0.3123</v>
@@ -766,10 +766,10 @@
         <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9995000000000001</v>
+        <v>-0.2014</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8486</v>
+        <v>-0.0505</v>
       </c>
       <c r="U4" t="n">
         <v>-0.1509</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ZHAO OLMOS</t>
+          <t>A. ARAGONES NAVAIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6867</v>
+        <v>-0.4666</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3963</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.083</v>
+        <v>-0.5598</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0025</v>
+        <v>-0.405</v>
       </c>
       <c r="H5" t="n">
-        <v>2.297</v>
+        <v>-0.3763</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.2994</v>
+        <v>-0.0287</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0277</v>
+        <v>1.2673</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5408</v>
+        <v>-0.0481</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.5131</v>
+        <v>1.3154</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0301</v>
+        <v>-1.6723</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2438</v>
+        <v>-0.3281</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7863</v>
+        <v>-1.3441</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2053</v>
+        <v>0.2053</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4173</v>
+        <v>0.0213</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2167</v>
+        <v>-0.1474</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.634</v>
+        <v>0.1687</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9384</v>
+        <v>-0.2883</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2402</v>
+        <v>-0.2883</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ARAGONES NAVAIS</t>
+          <t>J. ZHAO OLMOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1008</v>
+        <v>-1.0549</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.0608</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.9941</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.405</v>
+        <v>-1.0025</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3763</v>
+        <v>2.297</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0287</v>
+        <v>-3.2994</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2673</v>
+        <v>0.0277</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0481</v>
+        <v>2.5408</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3154</v>
+        <v>-2.5131</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6723</v>
+        <v>-1.0301</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3281</v>
+        <v>-0.2438</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3441</v>
+        <v>-0.7863</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2053</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6129</v>
+        <v>-0.7855</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8409</v>
+        <v>-0.2404</v>
       </c>
       <c r="U6" t="n">
-        <v>0.228</v>
+        <v>-0.5451</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2883</v>
+        <v>0.9384</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2883</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4817</v>
+        <v>-1.4628</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5897</v>
+        <v>0.3417</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0713</v>
+        <v>-1.8045</v>
       </c>
       <c r="G7" t="n">
         <v>1.96</v>
@@ -1000,13 +1000,13 @@
         <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.415</v>
+        <v>-0.3961</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1509</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5659</v>
+        <v>-0.2991</v>
       </c>
       <c r="V7" t="n">
         <v>-1.1786</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0792</v>
+        <v>-1.9383</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1461</v>
+        <v>0.0244</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9331</v>
+        <v>-1.9627</v>
       </c>
       <c r="G8" t="n">
         <v>-3.2559</v>
@@ -1078,13 +1078,13 @@
         <v>0.616</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5699</v>
+        <v>-0.4291</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4147</v>
+        <v>-0.2443</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1552</v>
+        <v>-0.1848</v>
       </c>
       <c r="V8" t="n">
         <v>1.1306</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5778</v>
+        <v>-1.9815</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3973</v>
+        <v>-1.9789</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1805</v>
+        <v>-0.0026</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4429</v>
@@ -1156,13 +1156,13 @@
         <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0868</v>
+        <v>0.5095</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2558</v>
+        <v>0.1626</v>
       </c>
       <c r="U9" t="n">
-        <v>0.169</v>
+        <v>0.3468</v>
       </c>
       <c r="V9" t="n">
         <v>-0.048</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8993</v>
+        <v>-4.4652</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.963</v>
+        <v>-3.44</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9363</v>
+        <v>-1.0252</v>
       </c>
       <c r="G10" t="n">
         <v>-1.488</v>
@@ -1234,13 +1234,13 @@
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.435</v>
+        <v>-0.0009</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5774</v>
+        <v>-0.0544</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1424</v>
+        <v>0.0535</v>
       </c>
       <c r="V10" t="n">
         <v>1.1306</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7537</v>
+        <v>-4.424200000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3182999999999998</v>
+        <v>0.6475999999999993</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.071899999999999</v>
+        <v>-5.0718</v>
       </c>
       <c r="G11" t="n">
         <v>-1.091900000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>6.682599999999999</v>
+        <v>6.6826</v>
       </c>
       <c r="I11" t="n">
         <v>-7.774500000000001</v>
@@ -1312,13 +1312,13 @@
         <v>9.240399999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7748000000000002</v>
+        <v>-0.4452999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5244999999999999</v>
+        <v>-0.1952</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2502000000000001</v>
+        <v>-0.2503</v>
       </c>
       <c r="V11" t="n">
         <v>3.2732</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.727</v>
+        <v>6.4505</v>
       </c>
       <c r="E12" t="n">
-        <v>3.8491</v>
+        <v>4.5813</v>
       </c>
       <c r="F12" t="n">
-        <v>1.878</v>
+        <v>1.8692</v>
       </c>
       <c r="G12" t="n">
         <v>4.2901</v>
@@ -1390,13 +1390,13 @@
         <v>2.6694</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9434</v>
+        <v>-0.2199</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.302</v>
+        <v>-0.5698</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3586</v>
+        <v>0.3499</v>
       </c>
       <c r="V12" t="n">
         <v>0.9429</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.621</v>
+        <v>3.3734</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3452</v>
+        <v>3.136</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2758</v>
+        <v>0.2374</v>
       </c>
       <c r="G13" t="n">
         <v>2.6099</v>
@@ -1468,13 +1468,13 @@
         <v>2.4641</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7183</v>
+        <v>0.4707</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6351</v>
+        <v>0.4259</v>
       </c>
       <c r="U13" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0447</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1179</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0354</v>
+        <v>2.4566</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5347</v>
+        <v>1.6979</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5007</v>
+        <v>0.7587</v>
       </c>
       <c r="G14" t="n">
         <v>0.0523</v>
@@ -1546,13 +1546,13 @@
         <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4233</v>
+        <v>0.8445</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1776</v>
+        <v>0.3408</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2458</v>
+        <v>0.5038</v>
       </c>
       <c r="V14" t="n">
         <v>0.1224</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2132</v>
+        <v>1.7642</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7166</v>
+        <v>1.0304</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4967</v>
+        <v>0.7338</v>
       </c>
       <c r="G15" t="n">
         <v>1.2234</v>
@@ -1624,13 +1624,13 @@
         <v>1.2321</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1244</v>
+        <v>-0.5734</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5851</v>
+        <v>-0.2713</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5393</v>
+        <v>-0.3021</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1179</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. MONTILLA DIAZ</t>
+          <t>K. GREELEY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0421</v>
+        <v>-0.6849</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3097</v>
+        <v>0.6226</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2676</v>
+        <v>-1.3075</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8896</v>
+        <v>-1.6761</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.3712</v>
+        <v>-0.8206</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4816</v>
+        <v>-0.8556</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.127</v>
+        <v>0.3012</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.9558</v>
+        <v>0.0915</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8288</v>
+        <v>0.2096</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7625999999999999</v>
+        <v>-1.9773</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4154</v>
+        <v>-0.9121</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3472</v>
+        <v>-1.0652</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2053</v>
+        <v>2.0534</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2321</v>
+        <v>2.2588</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8824</v>
+        <v>0.2208</v>
       </c>
       <c r="T16" t="n">
-        <v>1.844</v>
+        <v>-0.1939</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0384</v>
+        <v>0.4147</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2402</v>
+        <v>-1.283</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.7207</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2402</v>
+        <v>-2.0037</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SANTANA LUCHORO</t>
+          <t>M. MONTILLA DIAZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5074</v>
+        <v>-0.8213</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1399</v>
+        <v>-1.3557</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6325</v>
+        <v>0.5344</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4978</v>
+        <v>-1.8896</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2586</v>
+        <v>-2.3712</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2391</v>
+        <v>0.4816</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7252</v>
+        <v>-1.127</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0409</v>
+        <v>-1.9558</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3157</v>
+        <v>0.8288</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7726</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2177</v>
+        <v>-0.4154</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5548</v>
+        <v>-0.3472</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
-        <v>0.616</v>
+        <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6064</v>
+        <v>1.1032</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8173</v>
+        <v>0.798</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7891</v>
+        <v>0.3052</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>J. SANTANA LUCHORO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1339</v>
+        <v>-1.0619</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1469</v>
+        <v>-1.5583</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0131</v>
+        <v>0.4965</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0048</v>
+        <v>-1.4978</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4864</v>
+        <v>-1.2586</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4816</v>
+        <v>-0.2391</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1631</v>
+        <v>-0.7252</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1236</v>
+        <v>-1.0409</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0395</v>
+        <v>0.3157</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1679</v>
+        <v>-0.7726</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6101</v>
+        <v>-0.2177</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4422</v>
+        <v>-0.5548</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.616</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.313</v>
+        <v>1.0519</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5851</v>
+        <v>0.3989</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2721</v>
+        <v>0.653</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8159999999999999</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. PEREZ RAMIREZ</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7477</v>
+        <v>-1.2664</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3634</v>
+        <v>-2.0423</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3843</v>
+        <v>0.7759</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0301</v>
+        <v>-0.0048</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2535</v>
+        <v>-0.4864</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2836</v>
+        <v>0.4816</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4074</v>
+        <v>0.1631</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3821</v>
+        <v>0.1236</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0253</v>
+        <v>0.0395</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3773</v>
+        <v>-0.1679</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6355</v>
+        <v>-0.6101</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2582</v>
+        <v>0.4422</v>
       </c>
       <c r="P19" t="n">
-        <v>0.616</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9795</v>
+        <v>-0.4456</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.4805</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4407</v>
+        <v>0.035</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4144</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6982</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4144</v>
+        <v>-0.1179</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. GREELEY</t>
+          <t>G. PEREZ RAMIREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9192</v>
+        <v>-1.3049</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2143</v>
+        <v>-0.2588</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.705</v>
+        <v>-1.0461</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6761</v>
+        <v>0.0301</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8206</v>
+        <v>-0.2535</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8556</v>
+        <v>0.2836</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3012</v>
+        <v>1.4074</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0915</v>
+        <v>1.3821</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2096</v>
+        <v>0.0253</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9773</v>
+        <v>-1.3773</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9121</v>
+        <v>-1.6355</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0652</v>
+        <v>0.2582</v>
       </c>
       <c r="P20" t="n">
-        <v>2.0534</v>
+        <v>0.616</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2588</v>
+        <v>1.8481</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0135</v>
+        <v>-0.5366</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0308</v>
+        <v>-0.4342</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0172</v>
+        <v>-0.1025</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.283</v>
+        <v>-1.4144</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7207</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.0037</v>
+        <v>-1.4144</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4928</v>
+        <v>-2.757</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1995</v>
+        <v>-0.7811</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2933</v>
+        <v>-1.9759</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0457</v>
@@ -2092,13 +2092,13 @@
         <v>0.4107</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.482</v>
+        <v>0.2537</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1822</v>
+        <v>0.2362</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2998</v>
+        <v>0.0175</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3491</v>
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>4.753500000000002</v>
+        <v>6.148299999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>5.071900000000001</v>
+        <v>5.071999999999998</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3182</v>
+        <v>1.0764</v>
       </c>
       <c r="G22" t="n">
         <v>1.091800000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-6.682600000000001</v>
+        <v>-6.6826</v>
       </c>
       <c r="I22" t="n">
         <v>7.774400000000001</v>
@@ -2161,7 +2161,7 @@
         <v>-0.4445000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>6.1603</v>
+        <v>6.160299999999999</v>
       </c>
       <c r="Q22" t="n">
         <v>-9.240399999999999</v>
@@ -2170,13 +2170,13 @@
         <v>15.4007</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7746000000000002</v>
+        <v>2.1693</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2500000000000003</v>
+        <v>0.2501000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5245</v>
+        <v>1.9192</v>
       </c>
       <c r="V22" t="n">
         <v>-3.2732</v>
